--- a/jogos_2025-05-05.xlsx
+++ b/jogos_2025-05-05.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,34 +669,34 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.63</v>
       </c>
-      <c r="M2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -708,31 +708,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '22']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45782.1875</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="AJ3" t="n">
         <v>2</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['19', '22']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45782.1875</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.97</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X7" t="n">
         <v>4.1</v>
       </c>
-      <c r="N7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="Y7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.1</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AA7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['77', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['84', '85']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.22</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['12', '45']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45782.33333333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>5.15</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>3.46</v>
       </c>
       <c r="O8" t="n">
-        <v>6.09</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>3.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
         <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['77', '90+2']</t>
+          <t>['8', '45+8', '75']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['84', '85']</t>
+          <t>['28', '38', '87', '90']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.33</v>
+        <v>1.62</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45782.33333333334</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1572,70 +1572,70 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>3.97</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.46</v>
+        <v>1.66</v>
       </c>
       <c r="O9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P9" t="n">
         <v>2.6</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2.5</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['8', '45+8', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['28', '38', '87', '90']</t>
+          <t>['12', '45']</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45782.33333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="X18" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['38', '70', '77']</t>
+          <t>['-1', '-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45782.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kallithea</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>13</v>
+      </c>
+      <c r="M19" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.8</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '43', '52', '54']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '90+3']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.57</v>
+        <v>4.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45782.5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.09</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1', '-1']</t>
+          <t>['38', '70', '77']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.25</v>
+        <v>3.64</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45782.5</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="M21" t="n">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG21" t="n">
@@ -3193,10 +3193,10 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45782.5</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>13</v>
-      </c>
-      <c r="M22" t="n">
-        <v>7</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Q22" t="n">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['16', '43', '52', '54']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['29', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>1.18</v>
+        <v>2.25</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45782.5</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,19 +3352,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Kallithea</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
         <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X23" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3441,14 +3441,14 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" t="n">
         <v>1.57</v>
@@ -3600,33 +3600,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="O25" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.4</v>
+        <v>3.67</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W25" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['59', '90+7']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45782.54166666666</v>
@@ -3729,35 +3729,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.65</v>
+        <v>6.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>2.04</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.77</v>
+        <v>3.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.21</v>
+        <v>1.58</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['9', '25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45782.54166666666</v>
@@ -3858,119 +3858,119 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3</v>
       </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['40', '62', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['7', '85']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45782.54166666666</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.95</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>1.41</v>
+        <v>2.65</v>
       </c>
       <c r="O28" t="n">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['9', '25']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.55</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['1', '52']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AI28" t="n">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45782.54166666666</v>
@@ -4126,16 +4126,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
@@ -4144,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.43</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="X29" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['40', '62', '90+6']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['59', '90+7']</t>
+          <t>['7', '85']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45782.54166666666</v>
@@ -4245,32 +4245,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
         <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.58</v>
+        <v>4.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="N30" t="n">
-        <v>6.1</v>
+        <v>1.41</v>
       </c>
       <c r="O30" t="n">
-        <v>2.04</v>
+        <v>5.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['1', '52']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.6</v>
+        <v>1.29</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45782.54166666666</v>
@@ -4503,119 +4503,119 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '90+4']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45782.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['71', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['1', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI33" t="n">
         <v>2.45</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45782.58333333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.43</v>
+        <v>1.38</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.97</v>
+        <v>7.2</v>
       </c>
       <c r="O34" t="n">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['49', '52']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.5</v>
+        <v>2.95</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45782.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Lamia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M35" t="n">
         <v>3.5</v>
       </c>
-      <c r="M35" t="n">
-        <v>3</v>
-      </c>
       <c r="N35" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="O35" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U35" t="n">
         <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X35" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['71', '90+4']</t>
+          <t>['33', '51']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['1', '90+1']</t>
+          <t>['15', '24', '41']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5019,70 +5019,70 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5106,10 +5106,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG36" t="n">
@@ -5128,10 +5128,10 @@
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,16 +5158,16 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['45+1', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5277,35 +5277,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3.44</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.69</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
         <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T38" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.85</v>
+        <v>3.44</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>4.69</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X39" t="n">
         <v>3</v>
       </c>
-      <c r="T39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.2</v>
       </c>
-      <c r="X39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['9', '81']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['49', '87']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="N40" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
         <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['37', '67']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.25</v>
       </c>
-      <c r="X40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kotwica Kołobrzeg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="M41" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>2.51</v>
+        <v>2.85</v>
       </c>
       <c r="O41" t="n">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.52</v>
-      </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U41" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V41" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.33</v>
       </c>
-      <c r="X41" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC41" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '81']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['57', '90+2']</t>
+          <t>['49', '87']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5793,26 +5793,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kotwica Kołobrzeg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>2</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.38</v>
+        <v>2.95</v>
       </c>
       <c r="M42" t="n">
-        <v>4.9</v>
+        <v>2.94</v>
       </c>
       <c r="N42" t="n">
-        <v>7.2</v>
+        <v>2.51</v>
       </c>
       <c r="O42" t="n">
-        <v>1.83</v>
+        <v>3.52</v>
       </c>
       <c r="P42" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>2.97</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AC42" t="n">
         <v>1.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['49', '52']</t>
+          <t>['57', '90+2']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.95</v>
+        <v>1.44</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45782.58333333334</v>
@@ -5922,119 +5922,119 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lamia</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="O43" t="n">
-        <v>6</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q43" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.5</v>
       </c>
-      <c r="S43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y43" t="n">
+      <c r="AI43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['33', '51']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['15', '24', '41']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45782.58333333334</v>
@@ -6825,29 +6825,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.29</v>
+        <v>4.3</v>
       </c>
       <c r="M50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S50" t="n">
         <v>3</v>
       </c>
-      <c r="N50" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T50" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="U50" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V50" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76', '77']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45782.65625</v>
@@ -6954,119 +6954,119 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P51" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y51" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.02</v>
-      </c>
       <c r="Z51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['76', '77']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ51" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45782.65625</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,23 +7351,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>1</v>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="M54" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N54" t="n">
-        <v>3.2</v>
+        <v>4.31</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P54" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="R54" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ54" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X54" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45782.66666666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,109 +7480,109 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>3</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V55" t="n">
         <v>1</v>
       </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N55" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P55" t="n">
+      <c r="W55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.51</v>
-      </c>
       <c r="Z55" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45782.66666666666</v>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.35</v>
+        <v>2.54</v>
       </c>
       <c r="M58" t="n">
-        <v>5.2</v>
+        <v>3.78</v>
       </c>
       <c r="N58" t="n">
-        <v>6.2</v>
+        <v>2.27</v>
       </c>
       <c r="O58" t="n">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="P58" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.75</v>
+        <v>2.56</v>
       </c>
       <c r="R58" t="n">
         <v>1.22</v>
       </c>
       <c r="S58" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U58" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X58" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['9', '57', '64']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ58" t="n">
         <v>1.73</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X58" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['18', '27', '79']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>['37', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45782.67708333334</v>
@@ -7996,109 +7996,109 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.54</v>
+        <v>1.35</v>
       </c>
       <c r="M59" t="n">
-        <v>3.78</v>
+        <v>5.2</v>
       </c>
       <c r="N59" t="n">
-        <v>2.27</v>
+        <v>6.2</v>
       </c>
       <c r="O59" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="P59" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.56</v>
+        <v>5.75</v>
       </c>
       <c r="R59" t="n">
         <v>1.22</v>
       </c>
       <c r="S59" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T59" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X59" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB59" t="n">
         <v>1.67</v>
       </c>
-      <c r="V59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X59" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA59" t="n">
+      <c r="AC59" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD59" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB59" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['9', '57', '64']</t>
+          <t>['18', '27', '79']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '90+1']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.73</v>
+        <v>3.4</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45782.67708333334</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>General Caballero JLM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="M61" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="O61" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="P61" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R61" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S61" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="T61" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V61" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="W61" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X61" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AA61" t="n">
         <v>5</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['24', '30']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45782.79166666666</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,25 +8383,25 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
         <v>1</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -8409,83 +8409,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N62" t="n">
-        <v>4.64</v>
+        <v>3.9</v>
       </c>
       <c r="O62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X62" t="n">
         <v>2.4</v>
       </c>
-      <c r="P62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S62" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T62" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X62" t="n">
-        <v>3.02</v>
-      </c>
       <c r="Y62" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.77</v>
+        <v>5</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['24', '30']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AJ62" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45782.79166666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,25 +8512,25 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>General Caballero JLM</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.73</v>
+        <v>1.88</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>2.7</v>
+        <v>4.64</v>
       </c>
       <c r="O63" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="P63" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R63" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S63" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="T63" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U63" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V63" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W63" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="X63" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AA63" t="n">
-        <v>5</v>
+        <v>3.77</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
         <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AI63" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45782.79166666666</v>
@@ -8641,25 +8641,25 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M64" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N64" t="n">
         <v>3.7</v>
       </c>
       <c r="O64" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="R64" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="S64" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="T64" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U64" t="n">
         <v>1.27</v>
       </c>
       <c r="V64" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W64" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X64" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AA64" t="n">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '90']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '36', '50']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45782.8125</v>
@@ -8770,25 +8770,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M65" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
         <v>3.7</v>
       </c>
       <c r="O65" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="P65" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="R65" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="S65" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="T65" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U65" t="n">
         <v>1.27</v>
       </c>
       <c r="V65" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W65" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="X65" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['24', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['21', '36', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45782.8125</v>
